--- a/assets/ESR Formations-Spain.xlsx
+++ b/assets/ESR Formations-Spain.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7CFA916-9F2B-478A-A058-1C95A2A5ABF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{D7CFA916-9F2B-478A-A058-1C95A2A5ABF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE09946-7E4D-43CF-A223-D92BE25A4B4F}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="165" windowWidth="26610" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
   <si>
     <t>Formation</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>SP Lanceros</t>
+  </si>
+  <si>
+    <t>SP Mixed</t>
   </si>
 </sst>
 </file>
@@ -398,10 +401,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -1188,92 +1187,116 @@
         <v>SP Lanceros</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C4">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:28" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C5">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>SP Vanguardia</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Mixed</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Brittle*</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="W2" t="s">
-        <v>13</v>
-      </c>
-      <c r="X2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>SP División</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Infantry</v>
       </c>
       <c r="C3" t="str">
         <v>Brittle*</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" t="s">
-        <v>13</v>
-      </c>
-      <c r="U3" t="s">
-        <v>13</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
         <v>13</v>
       </c>
       <c r="W3" t="s">
@@ -1297,30 +1320,89 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
+        <v>SP División</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Infantry</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Brittle*</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" t="s">
+        <v>13</v>
+      </c>
+      <c r="U4" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" t="s">
+        <v>13</v>
+      </c>
+      <c r="W4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
         <v>SP Caballería Brigada</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="P4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R4" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="P5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB5" t="s">
         <v>13</v>
       </c>
     </row>
